--- a/data/trans_camb/IP41-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 13,94</t>
+          <t>-3,41; 14,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 10,43</t>
+          <t>-10,0; 10,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-93,39; -79,67</t>
+          <t>-93,61; -79,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 16,68</t>
+          <t>-3,63; 14,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 9,71</t>
+          <t>-10,66; 9,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,21; -76,97</t>
+          <t>-92,5; -76,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,82</t>
+          <t>-1,41; 11,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,49</t>
+          <t>-8,57; 6,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-91,22; -81,21</t>
+          <t>-91,25; -81,13</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 17,39</t>
+          <t>-3,45; 18,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 12,79</t>
+          <t>-11,02; 12,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 21,12</t>
+          <t>-3,94; 18,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 12,29</t>
+          <t>-12,09; 12,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 14,26</t>
+          <t>-1,5; 14,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 7,86</t>
+          <t>-9,55; 7,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 7,17</t>
+          <t>-5,67; 7,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 3,34</t>
+          <t>-11,24; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-94,93; -84,6</t>
+          <t>-94,78; -84,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 1,42</t>
+          <t>-11,28; 1,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -6,67</t>
+          <t>-22,29; -6,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-96,17; -87,79</t>
+          <t>-95,68; -87,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,43</t>
+          <t>-6,83; 2,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -4,42</t>
+          <t>-14,85; -4,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-94,35; -87,6</t>
+          <t>-94,58; -87,82</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 8,53</t>
+          <t>-6,08; 9,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 3,81</t>
+          <t>-12,0; 3,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 1,59</t>
+          <t>-11,93; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; -7,44</t>
+          <t>-23,55; -7,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 2,73</t>
+          <t>-7,47; 2,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -4,9</t>
+          <t>-16,08; -4,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 3,18</t>
+          <t>-12,29; 3,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -3,76</t>
+          <t>-22,83; -3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-97,85; -87,77</t>
+          <t>-97,87; -88,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,3</t>
+          <t>-9,75; 4,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,81; -2,42</t>
+          <t>-18,95; -1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,33; -87,51</t>
+          <t>-97,3; -87,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,71</t>
+          <t>-8,56; 2,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -5,4</t>
+          <t>-18,34; -5,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-96,66; -90,25</t>
+          <t>-96,92; -89,73</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 3,31</t>
+          <t>-12,76; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,93; -4,25</t>
+          <t>-23,98; -4,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,69</t>
+          <t>-10,11; 4,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -2,77</t>
+          <t>-19,86; -1,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,87</t>
+          <t>-8,88; 2,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -5,89</t>
+          <t>-19,23; -5,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 3,53</t>
+          <t>-11,7; 4,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 4,48</t>
+          <t>-11,72; 4,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-95,76; -83,73</t>
+          <t>-96,01; -84,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 2,03</t>
+          <t>-12,9; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 1,88</t>
+          <t>-13,31; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-96,85; -87,85</t>
+          <t>-97,23; -87,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 1,55</t>
+          <t>-9,97; 1,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 1,16</t>
+          <t>-9,69; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-95,77; -88,79</t>
+          <t>-95,61; -88,55</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 4,08</t>
+          <t>-12,32; 5,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 5,07</t>
+          <t>-12,84; 4,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 2,31</t>
+          <t>-13,73; 3,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 2,11</t>
+          <t>-13,91; 2,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,71</t>
+          <t>-10,63; 1,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 1,24</t>
+          <t>-10,19; 1,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 15,32</t>
+          <t>-7,22; 15,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 16,94</t>
+          <t>-2,71; 17,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-93,8; -77,57</t>
+          <t>-93,68; -76,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -0,13</t>
+          <t>-21,88; -1,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -1,46</t>
+          <t>-22,77; -1,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-98,48; -87,33</t>
+          <t>-98,48; -87,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 4,51</t>
+          <t>-11,17; 3,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 4,68</t>
+          <t>-11,5; 4,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-95,35; -84,95</t>
+          <t>-95,38; -85,43</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 19,57</t>
+          <t>-7,74; 19,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 21,63</t>
+          <t>-2,86; 22,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,24; -0,75</t>
+          <t>-22,96; -1,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -1,61</t>
+          <t>-24,04; -2,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 5,13</t>
+          <t>-11,87; 4,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 5,32</t>
+          <t>-12,05; 4,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 15,52</t>
+          <t>-2,83; 14,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 5,5</t>
+          <t>-15,99; 6,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -78,69</t>
+          <t>-93,91; -79,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 3,5</t>
+          <t>-12,57; 4,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 2,98</t>
+          <t>-14,37; 3,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -86,72</t>
+          <t>-96,88; -85,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 6,29</t>
+          <t>-5,32; 7,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 2,08</t>
+          <t>-12,67; 1,87</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-94,4; -85,58</t>
+          <t>-94,03; -85,54</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 19,58</t>
+          <t>-2,8; 18,88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 6,45</t>
+          <t>-17,37; 7,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 3,84</t>
+          <t>-13,18; 4,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 3,17</t>
+          <t>-15,27; 3,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 7,11</t>
+          <t>-5,7; 8,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 2,33</t>
+          <t>-13,64; 2,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 0,26</t>
+          <t>-11,82; -0,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-28,12; -13,4</t>
+          <t>-27,56; -13,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-96,11; -88,19</t>
+          <t>-96,06; -88,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 2,37</t>
+          <t>-8,9; 2,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -7,35</t>
+          <t>-20,47; -7,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-95,59; -88,42</t>
+          <t>-95,53; -88,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,28</t>
+          <t>-8,78; -0,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-21,99; -11,66</t>
+          <t>-22,3; -12,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-95,01; -89,59</t>
+          <t>-95,01; -89,78</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 0,27</t>
+          <t>-12,5; -0,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -14,99</t>
+          <t>-29,42; -14,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,58</t>
+          <t>-9,43; 2,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,94; -8,25</t>
+          <t>-21,7; -8,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -0,37</t>
+          <t>-9,28; -0,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,52; -12,95</t>
+          <t>-24,01; -13,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 0,19</t>
+          <t>-11,39; -0,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 2,55</t>
+          <t>-7,91; 2,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-94,61; -87,44</t>
+          <t>-94,69; -87,38</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -1,47</t>
+          <t>-12,55; -1,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 0,95</t>
+          <t>-9,42; 0,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-95,64; -88,39</t>
+          <t>-95,33; -88,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,01; -2,34</t>
+          <t>-9,64; -2,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -0,21</t>
+          <t>-7,24; 0,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-94,33; -89,23</t>
+          <t>-94,11; -89,36</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 0,2</t>
+          <t>-12,07; -0,27</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,83</t>
+          <t>-8,61; 3,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -1,61</t>
+          <t>-13,17; -1,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 1,01</t>
+          <t>-10,0; 0,75</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -2,6</t>
+          <t>-10,29; -2,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -0,23</t>
+          <t>-7,72; 0,28</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,7</t>
+          <t>-4,45; 0,57</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -3,9</t>
+          <t>-10,16; -4,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -89,19</t>
+          <t>-92,77; -89,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -1,64</t>
+          <t>-6,67; -1,7</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -5,66</t>
+          <t>-11,36; -5,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-93,89; -90,54</t>
+          <t>-93,81; -90,74</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,49</t>
+          <t>-4,98; -1,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -5,87</t>
+          <t>-9,73; -5,93</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-92,95; -90,5</t>
+          <t>-92,92; -90,55</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,77</t>
+          <t>-4,85; 0,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -4,37</t>
+          <t>-11,04; -4,66</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -1,83</t>
+          <t>-7,12; -1,88</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -6,19</t>
+          <t>-12,27; -6,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -1,64</t>
+          <t>-5,36; -1,51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -6,43</t>
+          <t>-10,44; -6,47</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">

--- a/data/trans_camb/IP41-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Provincia-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-87,84</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-85,69</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,23</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-0,62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-86,7</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 14,69</t>
+          <t>-2,41; 15,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 10,04</t>
+          <t>-9,43; 10,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-93,61; -79,46</t>
+          <t>-3,47; 15,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 14,46</t>
+          <t>-12,37; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 9,89</t>
+          <t>-1,19; 11,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,5; -76,04</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 11,72</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-8,57; 6,65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-91,25; -81,13</t>
+          <t>-8,14; 6,96</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>-0,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-0,86%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-0,71%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 18,22</t>
+          <t>-2,6; 19,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 12,48</t>
+          <t>-10,32; 13,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,65; 20,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 18,36</t>
+          <t>-14,11; 11,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 12,25</t>
+          <t>-1,31; 13,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,5; 14,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-9,55; 7,84</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-9,23; 8,23</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-90,63</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-14,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-14,76</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-92,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>-9,62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-91,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 7,79</t>
+          <t>-5,94; 7,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 3,49</t>
+          <t>-11,3; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-94,78; -84,97</t>
+          <t>-11,41; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 1,0</t>
+          <t>-22,45; -6,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,29; -6,62</t>
+          <t>-6,72; 2,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-95,68; -87,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-6,83; 2,48</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-14,85; -4,35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-94,58; -87,82</t>
+          <t>-14,88; -4,09</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-5,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,39%</t>
+          <t>-15,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-15,98%</t>
+          <t>-2,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>-10,51%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 9,06</t>
+          <t>-6,32; 8,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 3,93</t>
+          <t>-12,12; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,25; 2,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 1,1</t>
+          <t>-23,88; -7,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,55; -7,37</t>
+          <t>-7,22; 2,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-7,47; 2,76</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,08; -4,94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-16,09; -4,75</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-94,49</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-10,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-93,71</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-11,63</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-94,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 3,42</t>
+          <t>-10,99; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -3,72</t>
+          <t>-22,88; -3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-97,87; -88,15</t>
+          <t>-9,6; 4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 4,27</t>
+          <t>-19,21; -2,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -1,34</t>
+          <t>-8,37; 1,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,3; -87,97</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,56; 2,05</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,34; -5,01</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-96,92; -89,73</t>
+          <t>-18,76; -5,08</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-2,42%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,42%</t>
+          <t>-10,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-10,85%</t>
+          <t>-3,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-3,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-12,36%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 3,61</t>
+          <t>-11,59; 4,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,98; -4,28</t>
+          <t>-23,75; -4,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,9; 4,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 4,7</t>
+          <t>-19,93; -2,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -1,47</t>
+          <t>-8,75; 2,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-8,88; 2,32</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-19,23; -5,5</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-19,65; -5,58</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-91,9</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,59</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-5,32</t>
+          <t>-4,23</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-93,39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-4,23</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-4,61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-92,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 4,56</t>
+          <t>-11,96; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 4,18</t>
+          <t>-11,7; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-96,01; -84,5</t>
+          <t>-12,87; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 2,75</t>
+          <t>-13,48; 2,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 1,99</t>
+          <t>-9,8; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-97,23; -87,64</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-9,97; 1,02</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-9,69; 1,43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-95,61; -88,55</t>
+          <t>-10,33; 1,01</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,91%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,91%</t>
+          <t>-5,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-5,69%</t>
+          <t>-4,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-4,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 5,11</t>
+          <t>-12,44; 4,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 4,7</t>
+          <t>-12,41; 4,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,44; 2,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 3,04</t>
+          <t>-14,4; 2,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 2,12</t>
+          <t>-10,34; 1,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-10,63; 1,14</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; 1,63</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,94; 1,06</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1227,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-87,09</t>
+          <t>-10,57</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,57</t>
+          <t>-11,39</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-11,39</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-95,23</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-3,28</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
           <t>-2,57</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-91,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 15,25</t>
+          <t>-6,2; 15,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 17,47</t>
+          <t>-3,72; 17,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-93,68; -76,65</t>
+          <t>-20,51; -0,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,88; -1,19</t>
+          <t>-22,72; -0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,77; -1,65</t>
+          <t>-10,88; 4,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-98,48; -87,31</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-11,17; 3,82</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-11,5; 4,42</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-95,38; -85,43</t>
+          <t>-9,8; 4,87</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1303,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-11,1%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-11,1%</t>
+          <t>-11,96%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-11,96%</t>
+          <t>-3,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-3,59%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
           <t>-2,82%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 19,29</t>
+          <t>-6,59; 19,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 22,45</t>
+          <t>-3,83; 22,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,43; -1,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -1,34</t>
+          <t>-23,35; -0,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,04; -2,2</t>
+          <t>-11,49; 4,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-11,87; 4,43</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-12,05; 4,85</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,41; 5,48</t>
         </is>
       </c>
     </row>
@@ -1714,37 +1383,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-87,9</t>
+          <t>-4,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-92,9</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
           <t>-4,76</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>-90,47</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 14,96</t>
+          <t>-2,29; 14,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 6,31</t>
+          <t>-15,15; 6,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-93,91; -79,31</t>
+          <t>-13,24; 3,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 4,09</t>
+          <t>-14,61; 3,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 3,55</t>
+          <t>-5,81; 6,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-96,88; -85,73</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 7,12</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-12,67; 1,87</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>-94,03; -85,54</t>
+          <t>-12,42; 2,09</t>
         </is>
       </c>
     </row>
@@ -1820,37 +1459,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,46%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-4,46%</t>
+          <t>-5,54%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-5,54%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
           <t>-5,26%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 18,88</t>
+          <t>-2,47; 18,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 7,39</t>
+          <t>-16,52; 8,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,02; 3,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 4,64</t>
+          <t>-15,5; 3,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 3,72</t>
+          <t>-6,11; 7,44</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 8,21</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-13,64; 2,12</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-13,48; 2,27</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1539,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-92,75</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-13,87</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-13,87</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-92,52</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
           <t>-17,16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-92,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -0,34</t>
+          <t>-11,99; -0,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,56; -13,25</t>
+          <t>-28,0; -13,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-96,06; -88,27</t>
+          <t>-8,07; 3,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 2,07</t>
+          <t>-21,29; -7,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -7,42</t>
+          <t>-7,94; -0,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -88,26</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-8,78; -0,08</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-22,3; -12,62</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-95,01; -89,78</t>
+          <t>-21,84; -12,03</t>
         </is>
       </c>
     </row>
@@ -2036,37 +1615,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-2,94%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-2,94%</t>
+          <t>-15,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-15,0%</t>
+          <t>-4,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-4,54%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
           <t>-18,53%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -0,38</t>
+          <t>-12,83; -0,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,42; -14,75</t>
+          <t>-29,94; -14,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,65; 3,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,24</t>
+          <t>-22,81; -8,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,7; -8,27</t>
+          <t>-8,5; -0,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; -0,06</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-24,01; -13,88</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-23,27; -13,26</t>
         </is>
       </c>
     </row>
@@ -2146,37 +1695,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-91,45</t>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-6,87</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-92,7</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-6,11</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
           <t>-3,63</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>-92,09</t>
         </is>
       </c>
     </row>
@@ -2189,47 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -0,3</t>
+          <t>-10,99; 0,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,8</t>
+          <t>-8,06; 2,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-94,69; -87,38</t>
+          <t>-12,46; -1,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -1,79</t>
+          <t>-9,9; 0,68</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 0,74</t>
+          <t>-10,21; -2,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-95,33; -88,6</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-9,64; -2,23</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-7,24; 0,27</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-94,11; -89,36</t>
+          <t>-7,14; 0,26</t>
         </is>
       </c>
     </row>
@@ -2252,37 +1771,22 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-7,41%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-7,41%</t>
+          <t>-4,85%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-4,85%</t>
+          <t>-6,64%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-6,64%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
           <t>-3,94%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,07; -0,27</t>
+          <t>-11,97; 0,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,13</t>
+          <t>-8,63; 2,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,16; -2,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -1,96</t>
+          <t>-10,5; 0,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 0,75</t>
+          <t>-10,93; -2,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-10,29; -2,32</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-7,72; 0,28</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,61; 0,29</t>
         </is>
       </c>
     </row>
@@ -2362,37 +1851,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-91,09</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-92,38</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
           <t>-7,79</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>-91,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,57</t>
+          <t>-4,54; 0,7</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -4,17</t>
+          <t>-9,95; -4,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -89,27</t>
+          <t>-6,67; -1,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,7</t>
+          <t>-11,45; -6,14</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,84</t>
+          <t>-4,9; -1,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-93,81; -90,74</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; -1,38</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; -5,93</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>-92,92; -90,55</t>
+          <t>-9,85; -5,86</t>
         </is>
       </c>
     </row>
@@ -2468,37 +1927,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-4,44%</t>
+          <t>-9,34%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-9,34%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-3,32%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
           <t>-8,49%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,63</t>
+          <t>-4,92; 0,77</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -4,66</t>
+          <t>-10,78; -4,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,15; -2,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,88</t>
+          <t>-12,24; -6,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -6,45</t>
+          <t>-5,32; -1,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; -1,51</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-10,44; -6,47</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,67; -6,47</t>
         </is>
       </c>
     </row>
@@ -2566,12 +1995,12 @@
   <mergeCells count="13">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A36:A39"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/IP41-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,74</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5,16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 15,4</t>
+          <t>-3,36; 16,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 10,64</t>
+          <t>-10,84; 9,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 15,8</t>
+          <t>-3,36; 13,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 9,28</t>
+          <t>-9,95; 10,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 11,21</t>
+          <t>-1,02; 11,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 6,96</t>
+          <t>-8,65; 6,49</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-0,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-0,56%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 19,24</t>
+          <t>-3,63; 21,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 13,09</t>
+          <t>-12,33; 12,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 20,38</t>
+          <t>-3,48; 17,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 11,41</t>
+          <t>-10,72; 12,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 13,55</t>
+          <t>-1,13; 14,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 8,23</t>
+          <t>-9,54; 7,86</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-14,76</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-4,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-14,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 7,41</t>
+          <t>-11,53; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 3,12</t>
+          <t>-23,1; -6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 2,15</t>
+          <t>-6,03; 7,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,45; -6,64</t>
+          <t>-12,0; 3,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,33</t>
+          <t>-6,69; 2,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -4,09</t>
+          <t>-15,22; -4,42</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-5,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-15,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-4,6%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,39%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 8,54</t>
+          <t>-12,27; 1,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 3,61</t>
+          <t>-24,63; -7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 2,36</t>
+          <t>-6,41; 8,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -7,52</t>
+          <t>-12,89; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,59</t>
+          <t>-7,12; 2,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -4,75</t>
+          <t>-16,23; -4,9</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-10,17</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-13,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 3,72</t>
+          <t>-9,57; 4,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,88; -3,74</t>
+          <t>-18,81; -2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 4,4</t>
+          <t>-11,87; 3,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -2,13</t>
+          <t>-23,13; -3,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 1,89</t>
+          <t>-8,18; 1,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -5,08</t>
+          <t>-18,43; -5,4</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,85%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-4,29%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-13,93%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,42%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-10,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 4,02</t>
+          <t>-10,05; 4,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -4,19</t>
+          <t>-20,08; -2,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 4,81</t>
+          <t>-12,36; 3,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -2,32</t>
+          <t>-23,93; -4,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 2,08</t>
+          <t>-8,61; 1,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,65; -5,58</t>
+          <t>-19,5; -5,89</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-3,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,85</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 3,93</t>
+          <t>-13,15; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 3,83</t>
+          <t>-13,01; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 2,37</t>
+          <t>-12,78; 3,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 2,06</t>
+          <t>-11,57; 4,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 1,12</t>
+          <t>-9,49; 1,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 1,01</t>
+          <t>-10,28; 1,16</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,91%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-5,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-4,18%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-4,19%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 4,74</t>
+          <t>-13,64; 2,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 4,55</t>
+          <t>-13,62; 2,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 2,59</t>
+          <t>-13,51; 4,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 2,22</t>
+          <t>-12,4; 5,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,24</t>
+          <t>-10,01; 1,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 1,06</t>
+          <t>-10,94; 1,24</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-10,57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-11,39</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>4,58</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>6,92</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-10,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-11,39</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 15,46</t>
+          <t>-20,15; -0,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 17,51</t>
+          <t>-21,8; -1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -0,97</t>
+          <t>-7,35; 15,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,72; -0,83</t>
+          <t>-2,65; 16,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 4,16</t>
+          <t>-10,72; 4,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,87</t>
+          <t>-9,78; 4,68</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-11,1%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,96%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-11,1%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-11,96%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 19,66</t>
+          <t>-21,24; -0,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 22,7</t>
+          <t>-22,26; -1,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,43; -1,16</t>
+          <t>-7,86; 19,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,35; -0,94</t>
+          <t>-2,82; 21,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 4,68</t>
+          <t>-11,33; 5,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 5,48</t>
+          <t>-10,44; 5,32</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,14</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>5,89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-4,37</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-4,14</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-5,15</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 14,9</t>
+          <t>-13,86; 3,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 6,64</t>
+          <t>-14,73; 2,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 3,54</t>
+          <t>-2,11; 15,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 3,05</t>
+          <t>-15,84; 5,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 6,46</t>
+          <t>-5,4; 6,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 2,09</t>
+          <t>-12,27; 2,08</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-4,46%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-5,54%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-4,46%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-5,54%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 18,55</t>
+          <t>-14,43; 3,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 8,11</t>
+          <t>-15,89; 3,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 3,94</t>
+          <t>-2,17; 19,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 3,36</t>
+          <t>-17,54; 6,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,44</t>
+          <t>-5,74; 7,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 2,27</t>
+          <t>-13,26; 2,33</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-2,72</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-13,87</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-5,76</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-20,61</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-13,87</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -0,06</t>
+          <t>-8,19; 2,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-28,0; -13,29</t>
+          <t>-20,33; -7,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 3,09</t>
+          <t>-12,28; 0,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -7,95</t>
+          <t>-28,12; -13,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -0,13</t>
+          <t>-8,34; -0,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -12,03</t>
+          <t>-21,99; -11,66</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-2,94%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-15,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-6,21%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-22,22%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-2,94%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-15,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -0,24</t>
+          <t>-8,81; 2,58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -14,68</t>
+          <t>-21,94; -8,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,44</t>
+          <t>-12,96; 0,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,81; -8,82</t>
+          <t>-29,95; -14,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,5; -0,15</t>
+          <t>-8,94; -0,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,27; -13,26</t>
+          <t>-23,52; -12,95</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-5,33</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-2,72</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-6,87</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 0,42</t>
+          <t>-12,33; -1,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,44</t>
+          <t>-10,17; 0,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -1,99</t>
+          <t>-11,32; 0,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 0,68</t>
+          <t>-8,23; 2,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -2,04</t>
+          <t>-10,01; -2,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,26</t>
+          <t>-7,46; -0,21</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-7,41%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-4,85%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-5,82%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-2,97%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-7,41%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-4,85%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 0,38</t>
+          <t>-13,2; -1,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,7</t>
+          <t>-10,7; 1,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -2,24</t>
+          <t>-12,14; 0,2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 0,78</t>
+          <t>-8,87; 2,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -2,24</t>
+          <t>-10,71; -2,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,29</t>
+          <t>-7,94; -0,23</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-8,63</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-1,92</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-6,9</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,7</t>
+          <t>-6,73; -1,64</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -4,04</t>
+          <t>-11,34; -5,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,85</t>
+          <t>-4,59; 0,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -6,14</t>
+          <t>-9,74; -3,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -1,3</t>
+          <t>-5,02; -1,49</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -5,86</t>
+          <t>-9,82; -5,87</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-4,44%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-9,34%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-7,57%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-4,44%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,77</t>
+          <t>-7,27; -1,83</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -4,48</t>
+          <t>-12,22; -6,19</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -2,01</t>
+          <t>-5,01; 0,77</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -6,73</t>
+          <t>-10,58; -4,37</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -1,43</t>
+          <t>-5,4; -1,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,47</t>
+          <t>-10,64; -6,43</t>
         </is>
       </c>
     </row>
